--- a/nursing/フォーマット/02_訪問看護記録様式/11_退院前カンファレンス記録.xlsx
+++ b/nursing/フォーマット/02_訪問看護記録様式/11_退院前カンファレンス記録.xlsx
@@ -26,46 +26,46 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <name val="Meiryo UI"/>
+      <name val="Meiryo"/>
       <b val="1"/>
-      <color rgb="FF0E7490"/>
-      <sz val="13"/>
+      <color rgb="00163A2B"/>
+      <sz val="16"/>
     </font>
     <font>
-      <name val="Meiryo UI"/>
-      <b val="1"/>
-      <color rgb="FF0E7490"/>
+      <name val="Meiryo"/>
+      <color rgb="005C665C"/>
       <sz val="9"/>
     </font>
     <font>
-      <name val="Meiryo UI"/>
+      <name val="Meiryo"/>
       <b val="1"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Meiryo UI"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Meiryo UI"/>
-      <b val="1"/>
-      <color rgb="FFFFFFFF"/>
+      <color rgb="00163A2B"/>
       <sz val="10"/>
     </font>
     <font>
-      <name val="Meiryo UI"/>
-      <b val="1"/>
-      <color rgb="FFFFFFFF"/>
-      <sz val="9"/>
+      <name val="Meiryo"/>
+      <color rgb="00283129"/>
+      <sz val="10"/>
     </font>
     <font>
-      <name val="Meiryo UI"/>
-      <i val="1"/>
-      <color rgb="FF6B7280"/>
-      <sz val="9"/>
+      <name val="Meiryo"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Meiryo"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Meiryo"/>
+      <color rgb="005C665C"/>
+      <sz val="10"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -74,21 +74,26 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFCFFAFE"/>
+        <fgColor rgb="00E4EFE7"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF0E7490"/>
+        <fgColor rgb="001F4D3A"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF8FAFC"/>
+        <fgColor rgb="00A9854A"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F6EDDA"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="5">
     <border>
       <left/>
       <right/>
@@ -97,44 +102,77 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
+      <bottom style="medium">
+        <color rgb="00A9854A"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00DAD3C2"/>
+      </left>
+      <right style="thin">
+        <color rgb="00DAD3C2"/>
+      </right>
+      <top style="thin">
+        <color rgb="00DAD3C2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00DAD3C2"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00A9854A"/>
+      </left>
+      <right style="thin">
+        <color rgb="00A9854A"/>
+      </right>
+      <top style="thin">
+        <color rgb="00A9854A"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00A9854A"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="00A9854A"/>
+      </left>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -498,261 +536,346 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:G21"/>
+  <dimension ref="A1:G30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
-    <col width="20" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
-    <row r="1" ht="26" customHeight="1">
+    <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>退院前カンファレンス記録</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="20" customHeight="1">
+    <row r="2" ht="16" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>【加算根拠】退院・退所加算（相談支援）/ 訪問看護情報提供療養費（Ⅰ・Ⅱ）/ 入院時情報連携加算 ← 参加記録が必須</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="22" customHeight="1">
-      <c r="A3" s="3" t="inlineStr">
-        <is>
-          <t>開催日時</t>
-        </is>
-      </c>
-      <c r="C3" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">　　年　月　日（　）　　時〜　　時</t>
-        </is>
-      </c>
-      <c r="E3" s="3" t="inlineStr">
-        <is>
-          <t>開催場所</t>
-        </is>
-      </c>
-      <c r="G3" s="4" t="inlineStr"/>
-    </row>
+          <t>入院先・本人家族・在宅サービスで退院後の支援を調整。退院時共同指導加算の根拠資料</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="n"/>
+      <c r="C2" s="3" t="n"/>
+      <c r="D2" s="3" t="n"/>
+      <c r="E2" s="3" t="n"/>
+      <c r="F2" s="3" t="n"/>
+      <c r="G2" s="3" t="n"/>
+    </row>
+    <row r="3" ht="8" customHeight="1"/>
     <row r="4" ht="22" customHeight="1">
-      <c r="A4" s="3" t="inlineStr">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>開催日時 / 場所</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="n"/>
+      <c r="C4" s="6" t="inlineStr"/>
+      <c r="D4" s="5" t="n"/>
+      <c r="E4" s="5" t="n"/>
+      <c r="F4" s="5" t="n"/>
+      <c r="G4" s="5" t="n"/>
+    </row>
+    <row r="5" ht="22" customHeight="1">
+      <c r="A5" s="4" t="inlineStr">
         <is>
           <t>利用者氏名</t>
         </is>
       </c>
-      <c r="C4" s="4" t="inlineStr">
-        <is>
-          <t>（様）</t>
-        </is>
-      </c>
-      <c r="E4" s="3" t="inlineStr">
-        <is>
-          <t>入院医療機関</t>
-        </is>
-      </c>
-      <c r="G4" s="4" t="inlineStr"/>
-    </row>
-    <row r="5" ht="22" customHeight="1">
-      <c r="A5" s="3" t="inlineStr">
-        <is>
-          <t>退院予定日</t>
-        </is>
-      </c>
-      <c r="C5" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">　　年　月　日</t>
-        </is>
-      </c>
-      <c r="E5" s="3" t="inlineStr">
-        <is>
-          <t>担当訪問看護師</t>
-        </is>
-      </c>
-      <c r="G5" s="4" t="inlineStr"/>
-    </row>
-    <row r="6" ht="28" customHeight="1">
-      <c r="A6" s="5" t="inlineStr">
+      <c r="B5" s="5" t="n"/>
+      <c r="C5" s="6" t="inlineStr"/>
+      <c r="D5" s="5" t="n"/>
+      <c r="E5" s="5" t="n"/>
+      <c r="F5" s="5" t="n"/>
+      <c r="G5" s="5" t="n"/>
+    </row>
+    <row r="6" ht="22" customHeight="1">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>入院医療機関 / 病棟</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="n"/>
+      <c r="C6" s="6" t="inlineStr"/>
+      <c r="D6" s="5" t="n"/>
+      <c r="E6" s="5" t="n"/>
+      <c r="F6" s="5" t="n"/>
+      <c r="G6" s="5" t="n"/>
+    </row>
+    <row r="7" ht="22" customHeight="1">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>退院（予定）日</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="n"/>
+      <c r="C7" s="6" t="inlineStr"/>
+      <c r="D7" s="5" t="n"/>
+      <c r="E7" s="5" t="n"/>
+      <c r="F7" s="5" t="n"/>
+      <c r="G7" s="5" t="n"/>
+    </row>
+    <row r="8" ht="8" customHeight="1"/>
+    <row r="9" ht="24" customHeight="1">
+      <c r="A9" s="7" t="inlineStr">
+        <is>
+          <t>出席者</t>
+        </is>
+      </c>
+      <c r="B9" s="8" t="n"/>
+      <c r="C9" s="8" t="n"/>
+      <c r="D9" s="8" t="n"/>
+      <c r="E9" s="8" t="n"/>
+      <c r="F9" s="8" t="n"/>
+      <c r="G9" s="8" t="n"/>
+    </row>
+    <row r="10" ht="22" customHeight="1">
+      <c r="A10" s="9" t="inlineStr">
+        <is>
+          <t>所属・機関</t>
+        </is>
+      </c>
+      <c r="B10" s="9" t="inlineStr">
+        <is>
+          <t>職種</t>
+        </is>
+      </c>
+      <c r="C10" s="9" t="inlineStr">
         <is>
           <t>氏名</t>
         </is>
       </c>
-      <c r="B6" s="5" t="inlineStr">
-        <is>
-          <t>所属機関</t>
-        </is>
-      </c>
-      <c r="C6" s="5" t="inlineStr">
-        <is>
-          <t>役割・職種</t>
-        </is>
-      </c>
-      <c r="D6" s="5" t="inlineStr">
-        <is>
-          <t>参加形態</t>
-        </is>
-      </c>
-      <c r="E6" s="6" t="inlineStr">
-        <is>
-          <t>備考</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="20" customHeight="1">
-      <c r="A7" s="4" t="inlineStr"/>
-      <c r="B7" s="4" t="inlineStr"/>
-      <c r="C7" s="4" t="inlineStr"/>
-      <c r="D7" s="4" t="inlineStr"/>
-      <c r="E7" s="4" t="inlineStr"/>
-    </row>
-    <row r="8" ht="20" customHeight="1">
-      <c r="A8" s="4" t="inlineStr"/>
-      <c r="B8" s="4" t="inlineStr"/>
-      <c r="C8" s="4" t="inlineStr"/>
-      <c r="D8" s="4" t="inlineStr"/>
-      <c r="E8" s="4" t="inlineStr"/>
-    </row>
-    <row r="9" ht="20" customHeight="1">
-      <c r="A9" s="4" t="inlineStr"/>
-      <c r="B9" s="4" t="inlineStr"/>
-      <c r="C9" s="4" t="inlineStr"/>
-      <c r="D9" s="4" t="inlineStr"/>
-      <c r="E9" s="4" t="inlineStr"/>
-    </row>
-    <row r="10" ht="20" customHeight="1">
-      <c r="A10" s="4" t="inlineStr"/>
-      <c r="B10" s="4" t="inlineStr"/>
-      <c r="C10" s="4" t="inlineStr"/>
-      <c r="D10" s="4" t="inlineStr"/>
-      <c r="E10" s="4" t="inlineStr"/>
+      <c r="D10" s="9" t="inlineStr">
+        <is>
+          <t>役割</t>
+        </is>
+      </c>
+      <c r="E10" s="9" t="inlineStr"/>
+      <c r="F10" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="G10" s="9" t="inlineStr"/>
     </row>
     <row r="11" ht="20" customHeight="1">
-      <c r="A11" s="4" t="inlineStr"/>
-      <c r="B11" s="4" t="inlineStr"/>
-      <c r="C11" s="4" t="inlineStr"/>
-      <c r="D11" s="4" t="inlineStr"/>
-      <c r="E11" s="4" t="inlineStr"/>
+      <c r="A11" s="6" t="n"/>
+      <c r="B11" s="6" t="n"/>
+      <c r="C11" s="6" t="n"/>
+      <c r="D11" s="6" t="n"/>
+      <c r="E11" s="6" t="n"/>
+      <c r="F11" s="6" t="n"/>
+      <c r="G11" s="6" t="n"/>
     </row>
     <row r="12" ht="20" customHeight="1">
-      <c r="A12" s="4" t="inlineStr"/>
-      <c r="B12" s="4" t="inlineStr"/>
-      <c r="C12" s="4" t="inlineStr"/>
-      <c r="D12" s="4" t="inlineStr"/>
-      <c r="E12" s="4" t="inlineStr"/>
+      <c r="A12" s="6" t="n"/>
+      <c r="B12" s="6" t="n"/>
+      <c r="C12" s="6" t="n"/>
+      <c r="D12" s="6" t="n"/>
+      <c r="E12" s="6" t="n"/>
+      <c r="F12" s="6" t="n"/>
+      <c r="G12" s="6" t="n"/>
     </row>
     <row r="13" ht="20" customHeight="1">
-      <c r="A13" s="7" t="inlineStr">
-        <is>
-          <t>【退院時の状態・引き継ぎ情報】</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="60" customHeight="1">
-      <c r="A14" s="8" t="inlineStr">
-        <is>
-          <t>・診断名・障害名：
-・現在の服薬：
-・医療処置：
-・ADL・機能レベル：
-・精神状態：</t>
-        </is>
-      </c>
+      <c r="A13" s="6" t="n"/>
+      <c r="B13" s="6" t="n"/>
+      <c r="C13" s="6" t="n"/>
+      <c r="D13" s="6" t="n"/>
+      <c r="E13" s="6" t="n"/>
+      <c r="F13" s="6" t="n"/>
+      <c r="G13" s="6" t="n"/>
+    </row>
+    <row r="14" ht="20" customHeight="1">
+      <c r="A14" s="6" t="n"/>
+      <c r="B14" s="6" t="n"/>
+      <c r="C14" s="6" t="n"/>
+      <c r="D14" s="6" t="n"/>
+      <c r="E14" s="6" t="n"/>
+      <c r="F14" s="6" t="n"/>
+      <c r="G14" s="6" t="n"/>
     </row>
     <row r="15" ht="20" customHeight="1">
-      <c r="A15" s="7" t="inlineStr">
-        <is>
-          <t>【退院後の訪問看護計画】</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="60" customHeight="1">
-      <c r="A16" s="8" t="inlineStr">
-        <is>
-          <t>・訪問頻度：週　回（当初2週間：週　回）
-・主な看護内容：
-・緊急時連絡体制：</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="20" customHeight="1">
-      <c r="A17" s="7" t="inlineStr">
-        <is>
-          <t>【関係機関との役割分担・連携事項】</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="50" customHeight="1">
-      <c r="A18" s="8" t="inlineStr">
-        <is>
-          <t>・訪問看護：
-・相談支援専門員：
-・居宅介護：
-・主治医：</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="20" customHeight="1">
-      <c r="A19" s="7" t="inlineStr">
-        <is>
-          <t>【退院後に必要な手続き・準備事項】</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="50" customHeight="1">
-      <c r="A20" s="8" t="inlineStr">
-        <is>
-          <t>・介護保険：申請済み / 未申請
-・自立支援医療：更新期限確認
-・障害福祉サービス：サービス等利用計画の更新</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="26" customHeight="1">
-      <c r="A21" s="9" t="inlineStr">
-        <is>
-          <t>記録者署名：　　　　　　　　　　　日付：　　年　月　日　　（本記録は5年間保管）</t>
-        </is>
-      </c>
+      <c r="A15" s="6" t="n"/>
+      <c r="B15" s="6" t="n"/>
+      <c r="C15" s="6" t="n"/>
+      <c r="D15" s="6" t="n"/>
+      <c r="E15" s="6" t="n"/>
+      <c r="F15" s="6" t="n"/>
+      <c r="G15" s="6" t="n"/>
+    </row>
+    <row r="16" ht="20" customHeight="1">
+      <c r="A16" s="6" t="n"/>
+      <c r="B16" s="6" t="n"/>
+      <c r="C16" s="6" t="n"/>
+      <c r="D16" s="6" t="n"/>
+      <c r="E16" s="6" t="n"/>
+      <c r="F16" s="6" t="n"/>
+      <c r="G16" s="6" t="n"/>
+    </row>
+    <row r="17" ht="8" customHeight="1"/>
+    <row r="18" ht="24" customHeight="1">
+      <c r="A18" s="7" t="inlineStr">
+        <is>
+          <t>病状・退院後の医療処置・指導内容</t>
+        </is>
+      </c>
+      <c r="B18" s="8" t="n"/>
+      <c r="C18" s="8" t="n"/>
+      <c r="D18" s="8" t="n"/>
+      <c r="E18" s="8" t="n"/>
+      <c r="F18" s="8" t="n"/>
+      <c r="G18" s="8" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="5" t="n"/>
+      <c r="B19" s="5" t="n"/>
+      <c r="C19" s="5" t="n"/>
+      <c r="D19" s="5" t="n"/>
+      <c r="E19" s="5" t="n"/>
+      <c r="F19" s="5" t="n"/>
+      <c r="G19" s="5" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="5" t="n"/>
+      <c r="B20" s="5" t="n"/>
+      <c r="C20" s="5" t="n"/>
+      <c r="D20" s="5" t="n"/>
+      <c r="E20" s="5" t="n"/>
+      <c r="F20" s="5" t="n"/>
+      <c r="G20" s="5" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="5" t="n"/>
+      <c r="B21" s="5" t="n"/>
+      <c r="C21" s="5" t="n"/>
+      <c r="D21" s="5" t="n"/>
+      <c r="E21" s="5" t="n"/>
+      <c r="F21" s="5" t="n"/>
+      <c r="G21" s="5" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="5" t="n"/>
+      <c r="B22" s="5" t="n"/>
+      <c r="C22" s="5" t="n"/>
+      <c r="D22" s="5" t="n"/>
+      <c r="E22" s="5" t="n"/>
+      <c r="F22" s="5" t="n"/>
+      <c r="G22" s="5" t="n"/>
+    </row>
+    <row r="23" ht="8" customHeight="1"/>
+    <row r="24" ht="24" customHeight="1">
+      <c r="A24" s="7" t="inlineStr">
+        <is>
+          <t>在宅での支援体制・役割分担・次回確認事項</t>
+        </is>
+      </c>
+      <c r="B24" s="8" t="n"/>
+      <c r="C24" s="8" t="n"/>
+      <c r="D24" s="8" t="n"/>
+      <c r="E24" s="8" t="n"/>
+      <c r="F24" s="8" t="n"/>
+      <c r="G24" s="8" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="5" t="n"/>
+      <c r="B25" s="5" t="n"/>
+      <c r="C25" s="5" t="n"/>
+      <c r="D25" s="5" t="n"/>
+      <c r="E25" s="5" t="n"/>
+      <c r="F25" s="5" t="n"/>
+      <c r="G25" s="5" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="5" t="n"/>
+      <c r="B26" s="5" t="n"/>
+      <c r="C26" s="5" t="n"/>
+      <c r="D26" s="5" t="n"/>
+      <c r="E26" s="5" t="n"/>
+      <c r="F26" s="5" t="n"/>
+      <c r="G26" s="5" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="5" t="n"/>
+      <c r="B27" s="5" t="n"/>
+      <c r="C27" s="5" t="n"/>
+      <c r="D27" s="5" t="n"/>
+      <c r="E27" s="5" t="n"/>
+      <c r="F27" s="5" t="n"/>
+      <c r="G27" s="5" t="n"/>
+    </row>
+    <row r="28" ht="22" customHeight="1">
+      <c r="A28" s="4" t="inlineStr">
+        <is>
+          <t>記録者</t>
+        </is>
+      </c>
+      <c r="B28" s="5" t="n"/>
+      <c r="C28" s="6" t="inlineStr"/>
+      <c r="D28" s="5" t="n"/>
+      <c r="E28" s="5" t="n"/>
+      <c r="F28" s="5" t="n"/>
+      <c r="G28" s="5" t="n"/>
+    </row>
+    <row r="29" ht="22" customHeight="1">
+      <c r="A29" s="4" t="inlineStr">
+        <is>
+          <t>退院時共同指導加算</t>
+        </is>
+      </c>
+      <c r="B29" s="5" t="n"/>
+      <c r="C29" s="10" t="inlineStr">
+        <is>
+          <t>□算定（特別管理対象は16,000円／通常8,000円）　□算定なし</t>
+        </is>
+      </c>
+      <c r="D29" s="5" t="n"/>
+      <c r="E29" s="5" t="n"/>
+      <c r="F29" s="5" t="n"/>
+      <c r="G29" s="5" t="n"/>
+    </row>
+    <row r="30" ht="20" customHeight="1">
+      <c r="A30" s="11" t="inlineStr">
+        <is>
+          <t>※ 退院時共同指導加算は、入院中に医療機関職員と共同で在宅療養上の指導を行い文書提供した場合に算定。</t>
+        </is>
+      </c>
+      <c r="B30" s="12" t="n"/>
+      <c r="C30" s="12" t="n"/>
+      <c r="D30" s="12" t="n"/>
+      <c r="E30" s="12" t="n"/>
+      <c r="F30" s="12" t="n"/>
+      <c r="G30" s="12" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="27">
-    <mergeCell ref="E10:G10"/>
-    <mergeCell ref="A14:G14"/>
-    <mergeCell ref="A17:G17"/>
-    <mergeCell ref="C5:D5"/>
-    <mergeCell ref="E5:F5"/>
-    <mergeCell ref="A20:G20"/>
-    <mergeCell ref="E9:G9"/>
-    <mergeCell ref="A19:G19"/>
-    <mergeCell ref="E6:G6"/>
-    <mergeCell ref="C4:D4"/>
-    <mergeCell ref="A13:G13"/>
-    <mergeCell ref="E4:F4"/>
-    <mergeCell ref="E11:G11"/>
-    <mergeCell ref="A15:G15"/>
-    <mergeCell ref="E7:G7"/>
-    <mergeCell ref="A3:B3"/>
+  <mergeCells count="18">
+    <mergeCell ref="A4:B4"/>
+    <mergeCell ref="C29:G29"/>
+    <mergeCell ref="C4:G4"/>
+    <mergeCell ref="C7:G7"/>
     <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A29:B29"/>
+    <mergeCell ref="A7:B7"/>
+    <mergeCell ref="A9:G9"/>
+    <mergeCell ref="C6:G6"/>
+    <mergeCell ref="A18:G18"/>
     <mergeCell ref="A5:B5"/>
-    <mergeCell ref="E12:G12"/>
-    <mergeCell ref="A16:G16"/>
-    <mergeCell ref="A4:B4"/>
-    <mergeCell ref="A18:G18"/>
-    <mergeCell ref="A21:G21"/>
-    <mergeCell ref="E8:G8"/>
+    <mergeCell ref="A28:B28"/>
+    <mergeCell ref="C28:G28"/>
+    <mergeCell ref="C5:G5"/>
     <mergeCell ref="A2:G2"/>
-    <mergeCell ref="C3:D3"/>
-    <mergeCell ref="E3:F3"/>
+    <mergeCell ref="A24:G24"/>
+    <mergeCell ref="A30:G30"/>
+    <mergeCell ref="A6:B6"/>
   </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.5" right="0.5" top="0.6" bottom="0.5" header="0.2" footer="0.2"/>
+  <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
 </file>